--- a/classdetails.xlsx
+++ b/classdetails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/clintguymon/Agents/gradtime/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{858B4B84-5E79-0F41-9CEB-70341EC1EE41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5CBB17-8C74-C849-8F89-95EDB5F143D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2020" yWindow="660" windowWidth="25820" windowHeight="18060" xr2:uid="{7AE83803-FA18-CC44-BB93-2F36850F4C7D}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="292">
   <si>
     <t>Topic</t>
   </si>
@@ -915,6 +915,9 @@
   </si>
   <si>
     <t>Arts, letters, and sciences</t>
+  </si>
+  <si>
+    <t>Fall, every other year</t>
   </si>
 </sst>
 </file>
@@ -1383,6 +1386,9 @@
       <c r="G2" t="s">
         <v>8</v>
       </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
       <c r="K2" t="s">
         <v>118</v>
       </c>
@@ -3025,7 +3031,7 @@
         <v>127</v>
       </c>
       <c r="G47" t="s">
-        <v>8</v>
+        <v>291</v>
       </c>
       <c r="K47" t="s">
         <v>43</v>
@@ -3185,7 +3191,7 @@
         <v>134</v>
       </c>
       <c r="G52" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>143</v>
